--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G20" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G20" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="M24" t="n">
-        <v>4.41</v>
+        <v>4.6</v>
       </c>
       <c r="N24" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3552,10 +3552,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK24"/>
+  <dimension ref="A1:AK25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3587,6 +3587,135 @@
       </c>
       <c r="AK24" s="3" t="n">
         <v>45911.58333333334</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45911</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Canada Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Valour FC</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Forge FC</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3" t="n">
+        <v>45911.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.54166666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.54166666666</v>
       </c>
     </row>
     <row r="22">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45911.54166666666</v>
+        <v>45911.5</v>
       </c>
     </row>
     <row r="21">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45911.54166666666</v>
+        <v>45911.5</v>
       </c>
     </row>
     <row r="22">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="M2" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="N2" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>3.28</v>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -678,34 +678,34 @@
         <v>3.62</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Y2" t="n">
         <v>1.8</v>
@@ -714,16 +714,16 @@
         <v>1.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -669,28 +669,28 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="M2" t="n">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="N2" t="n">
-        <v>3.62</v>
+        <v>3.75</v>
       </c>
       <c r="O2" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="P2" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.83</v>
+        <v>4.2</v>
       </c>
       <c r="R2" t="n">
         <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
         <v>2.5</v>
@@ -699,7 +699,7 @@
         <v>1.5</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
         <v>1.18</v>
@@ -708,22 +708,22 @@
         <v>3.92</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AA2" t="n">
         <v>2.67</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AC2" t="n">
         <v>1.65</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AH2" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="M3" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3516,40 +3516,40 @@
         <v>1.57</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AA24" t="n">
         <v>2.05</v>
@@ -3558,10 +3558,10 @@
         <v>1.77</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK25"/>
+  <dimension ref="A1:AK20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.54166666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.54166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.54166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.54166666666</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.54166666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.54166666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.55208333334</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.55208333334</v>
       </c>
     </row>
     <row r="19">
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.58333333334</v>
       </c>
     </row>
     <row r="20">
@@ -2950,27 +2950,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,651 +3070,6 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45911.5</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Monastir</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Etoile du Sahel</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" s="3" t="n">
-        <v>45911.5</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>UAE Arabian Gulf League</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Shabab Al Ahli Dubai</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Bani Yas</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" s="3" t="n">
-        <v>45911.55208333334</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>UAE Arabian Gulf League</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Al Khaleej</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Al Sharjah</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" s="3" t="n">
-        <v>45911.55208333334</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Iceland Úrvalsdeild</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>ÍA</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Breidablik</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="O24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X24" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="3" t="n">
-        <v>45911.58333333334</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Valour FC</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Forge FC</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" s="3" t="n">
         <v>45911.875</v>
       </c>
     </row>

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="M2" t="n">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="N2" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="O2" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.2</v>
+        <v>4.57</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
         <v>2.5</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X2" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AA2" t="n">
         <v>2.67</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="N3" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="O3" t="n">
-        <v>3.41</v>
+        <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="R3" t="n">
         <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U3" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X3" t="n">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AB3" t="n">
         <v>1.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.43</v>
+        <v>1.41</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>6.75</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45911.54166666666</v>
+        <v>45911.5</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45911.54166666666</v>
+        <v>45911.5</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45911.54166666666</v>
+        <v>45911.5</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45911.54166666666</v>
+        <v>45911.5</v>
       </c>
     </row>
     <row r="13">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45911.54166666666</v>
+        <v>45911.5</v>
       </c>
     </row>
     <row r="14">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45911.54166666666</v>
+        <v>45911.5</v>
       </c>
     </row>
     <row r="15">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45911.54166666666</v>
+        <v>45911.5</v>
       </c>
     </row>
     <row r="16">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2508,10 +2508,10 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45911.54166666666</v>
+        <v>45911.5</v>
       </c>
     </row>
     <row r="17">
@@ -2871,40 +2871,40 @@
         <v>1.57</v>
       </c>
       <c r="O19" t="n">
-        <v>4.5</v>
+        <v>3.69</v>
       </c>
       <c r="P19" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
         <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="T19" t="n">
         <v>2.04</v>
       </c>
       <c r="U19" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="Y19" t="n">
         <v>1.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AA19" t="n">
         <v>2.05</v>
@@ -2916,7 +2916,7 @@
         <v>1.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
         <v>1.16</v>

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK20"/>
+  <dimension ref="A1:AK19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.54166666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.54166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.54166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.54166666666</v>
       </c>
     </row>
     <row r="15">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.54166666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2508,10 +2508,10 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.55208333334</v>
       </c>
     </row>
     <row r="17">
@@ -2692,27 +2692,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45911.55208333334</v>
+        <v>45911.58333333334</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,135 +2941,6 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45911.58333333334</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Valour FC</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Forge FC</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" s="3" t="n">
         <v>45911.875</v>
       </c>
     </row>

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK19"/>
+  <dimension ref="A1:AK15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45911.54166666666</v>
+        <v>45911.55208333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45911.54166666666</v>
+        <v>45911.55208333334</v>
       </c>
     </row>
     <row r="14">
@@ -2176,27 +2176,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45911.54166666666</v>
+        <v>45911.58333333334</v>
       </c>
     </row>
     <row r="15">
@@ -2305,27 +2305,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,522 +2425,6 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45911.54166666666</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>UAE Arabian Gulf League</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Al Khaleej</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Al Sharjah</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" s="3" t="n">
-        <v>45911.55208333334</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>UAE Arabian Gulf League</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Shabab Al Ahli Dubai</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Bani Yas</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" s="3" t="n">
-        <v>45911.55208333334</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Iceland Úrvalsdeild</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>ÍA</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Breidablik</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" s="3" t="n">
-        <v>45911.58333333334</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Valour FC</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Forge FC</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" s="3" t="n">
         <v>45911.875</v>
       </c>
     </row>

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK15"/>
+  <dimension ref="A1:AK14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>3.62</v>
       </c>
       <c r="O2" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="P2" t="n">
         <v>2.3</v>
@@ -696,7 +696,7 @@
         <v>2.5</v>
       </c>
       <c r="U2" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="V2" t="n">
         <v>1.03</v>
@@ -705,7 +705,7 @@
         <v>1.2</v>
       </c>
       <c r="X2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y2" t="n">
         <v>1.8</v>
@@ -714,16 +714,16 @@
         <v>1.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="AB2" t="n">
         <v>1.44</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
         <v>2.42</v>
       </c>
       <c r="O3" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="R3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
         <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="U3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
@@ -834,7 +834,7 @@
         <v>1.34</v>
       </c>
       <c r="X3" t="n">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="Y3" t="n">
         <v>2.03</v>
@@ -849,10 +849,10 @@
         <v>1.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>1.27</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45911.54166666666</v>
+        <v>45911.5</v>
       </c>
     </row>
     <row r="10">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.43</v>
+        <v>1.37</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>3.63</v>
       </c>
       <c r="N10" t="n">
-        <v>2.8</v>
+        <v>6.13</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>7.48</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="X10" t="n">
-        <v>2.48</v>
+        <v>3.08</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45911.54166666666</v>
+        <v>45911.55208333334</v>
       </c>
     </row>
     <row r="12">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45911.55208333334</v>
+        <v>45911.58333333334</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2296,135 +2296,6 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45911.58333333334</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Valour FC</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Forge FC</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="3" t="n">
         <v>45911.875</v>
       </c>
     </row>

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -669,22 +669,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="M2" t="n">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="N2" t="n">
-        <v>3.62</v>
+        <v>3.95</v>
       </c>
       <c r="O2" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="R2" t="n">
         <v>1.32</v>
@@ -696,28 +696,28 @@
         <v>2.5</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="V2" t="n">
         <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X2" t="n">
         <v>4.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AA2" t="n">
         <v>2.62</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AC2" t="n">
         <v>1.62</v>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH2" t="n">
         <v>2</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
       <c r="M3" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="O3" t="n">
         <v>3.3</v>
@@ -813,7 +813,7 @@
         <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="R3" t="n">
         <v>1.42</v>
@@ -837,10 +837,10 @@
         <v>3.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AA3" t="n">
         <v>3.6</v>
@@ -852,7 +852,7 @@
         <v>1.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="M13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="N13" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="O13" t="n">
         <v>3.69</v>
@@ -2112,7 +2112,7 @@
         <v>3.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="U13" t="n">
         <v>1.73</v>
@@ -2121,10 +2121,10 @@
         <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="Y13" t="n">
         <v>1.4</v>
@@ -2133,16 +2133,16 @@
         <v>2.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AC13" t="n">
         <v>1.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45911.54166666666</v>
+        <v>45911.5</v>
       </c>
     </row>
     <row r="10">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="M10" t="n">
-        <v>3.63</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
         <v>6.13</v>
       </c>
       <c r="O10" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.48</v>
+        <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="U10" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
         <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X10" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK14"/>
+  <dimension ref="A1:AK20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,55 +669,55 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="M2" t="n">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="N2" t="n">
-        <v>3.95</v>
+        <v>3.62</v>
       </c>
       <c r="O2" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U2" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="V2" t="n">
         <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X2" t="n">
         <v>4.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AC2" t="n">
         <v>1.62</v>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AH2" t="n">
         <v>2</v>
@@ -798,34 +798,34 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.59</v>
+        <v>2.49</v>
       </c>
       <c r="M3" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q3" t="n">
         <v>3.1</v>
       </c>
-      <c r="N3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="O3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.12</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="T3" t="n">
         <v>2.99</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
@@ -834,13 +834,13 @@
         <v>1.34</v>
       </c>
       <c r="X3" t="n">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AA3" t="n">
         <v>3.6</v>
@@ -852,7 +852,7 @@
         <v>1.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>1.27</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45911.54166666666</v>
+        <v>45911.5</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45911.55208333334</v>
+        <v>45911.5</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45911.55208333334</v>
+        <v>45911.5</v>
       </c>
     </row>
     <row r="13">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45911.58333333334</v>
+        <v>45911.5</v>
       </c>
     </row>
     <row r="14">
@@ -2176,126 +2176,900 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Tunisia Ligue 1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Kairouan</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Marsa</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="n">
+        <v>45911.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45911</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Ben Aknoun</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Paradou AC</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3" t="n">
+        <v>45911.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45911</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Oued Akbou</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>MC Alger</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="3" t="n">
+        <v>45911.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45911</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>UAE Arabian Gulf League</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Al Khaleej</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Al Sharjah</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="3" t="n">
+        <v>45911.55208333334</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45911</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>UAE Arabian Gulf League</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Shabab Al Ahli Dubai</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bani Yas</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="3" t="n">
+        <v>45911.55208333334</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45911</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Iceland Úrvalsdeild</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ÍA</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Breidablik</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="3" t="n">
+        <v>45911.58333333334</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45911</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Canada Canadian Premier League</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Valour FC</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Forge FC</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="3" t="n">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3" t="n">
         <v>45911.875</v>
       </c>
     </row>

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK20"/>
+  <dimension ref="A1:AK14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.43</v>
+        <v>1.37</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>3.63</v>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>6.13</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="X9" t="n">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.55208333334</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.55208333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.58333333334</v>
       </c>
     </row>
     <row r="14">
@@ -2176,27 +2176,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,780 +2296,6 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45911.5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Ben Aknoun</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Paradou AC</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="3" t="n">
-        <v>45911.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Oued Akbou</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>MC Alger</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" s="3" t="n">
-        <v>45911.5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>UAE Arabian Gulf League</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Al Khaleej</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Al Sharjah</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" s="3" t="n">
-        <v>45911.55208333334</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>UAE Arabian Gulf League</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Shabab Al Ahli Dubai</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Bani Yas</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" s="3" t="n">
-        <v>45911.55208333334</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Iceland Úrvalsdeild</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>ÍA</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Breidablik</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="O19" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" s="3" t="n">
-        <v>45911.58333333334</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Valour FC</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Forge FC</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" s="3" t="n">
         <v>45911.875</v>
       </c>
     </row>

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -678,16 +678,16 @@
         <v>3.62</v>
       </c>
       <c r="O2" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S2" t="n">
         <v>3.2</v>
@@ -714,16 +714,16 @@
         <v>1.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="AB2" t="n">
         <v>1.44</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AH2" t="n">
         <v>2</v>
@@ -807,25 +807,25 @@
         <v>2.42</v>
       </c>
       <c r="O3" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="R3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>2.99</v>
+        <v>3.12</v>
       </c>
       <c r="U3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
@@ -834,7 +834,7 @@
         <v>1.34</v>
       </c>
       <c r="X3" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="n">
         <v>2.03</v>
@@ -849,10 +849,10 @@
         <v>1.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>1.27</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.37</v>
+        <v>2.46</v>
       </c>
       <c r="M9" t="n">
-        <v>3.63</v>
+        <v>2.95</v>
       </c>
       <c r="N9" t="n">
-        <v>6.13</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>2.48</v>
       </c>
       <c r="Y9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45911.54166666666</v>
+        <v>45911.5</v>
       </c>
     </row>
     <row r="10">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.43</v>
+        <v>1.41</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="N10" t="n">
-        <v>2.8</v>
+        <v>6.8</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="X10" t="n">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1875,10 +1875,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2097,13 +2097,13 @@
         <v>1.57</v>
       </c>
       <c r="O13" t="n">
-        <v>4.87</v>
+        <v>4.9</v>
       </c>
       <c r="P13" t="n">
         <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R13" t="n">
         <v>1.22</v>
@@ -2112,10 +2112,10 @@
         <v>3.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="U13" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="V13" t="n">
         <v>1.01</v>
@@ -2124,13 +2124,13 @@
         <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>5.5</v>
+        <v>5.65</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="AA13" t="n">
         <v>2.05</v>
@@ -2139,10 +2139,10 @@
         <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -669,58 +669,58 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="M2" t="n">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="N2" t="n">
-        <v>3.62</v>
+        <v>3.95</v>
       </c>
       <c r="O2" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="R2" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="V2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
         <v>1.2</v>
       </c>
       <c r="X2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AD2" t="n">
         <v>2.19</v>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -798,49 +798,49 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.49</v>
+        <v>2.94</v>
       </c>
       <c r="M3" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="N3" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
         <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="U3" t="n">
         <v>1.33</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X3" t="n">
         <v>3</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AA3" t="n">
         <v>3.6</v>
@@ -849,10 +849,10 @@
         <v>1.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1572,37 +1572,37 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W9" t="n">
         <v>1.46</v>
@@ -1611,22 +1611,22 @@
         <v>2.48</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45911.5</v>
+        <v>45911.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
         <v>6.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="P10" t="n">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S10" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="T10" t="n">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="U10" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.27</v>
+        <v>2.36</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.16</v>
+        <v>4.05</v>
       </c>
       <c r="M11" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>9.75</v>
+        <v>1.6</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1875,10 +1875,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2004,10 +2004,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2088,19 +2088,19 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.1</v>
+        <v>4.75</v>
       </c>
       <c r="M13" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="O13" t="n">
         <v>4.9</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q13" t="n">
         <v>1.98</v>
@@ -2109,40 +2109,40 @@
         <v>1.22</v>
       </c>
       <c r="S13" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T13" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="V13" t="n">
         <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
         <v>5.65</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
         <v>1.53</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>1.19</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,77 +1572,77 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>2.85</v>
+        <v>6.8</v>
       </c>
       <c r="O9" t="n">
-        <v>3.35</v>
+        <v>1.99</v>
       </c>
       <c r="P9" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.75</v>
+        <v>7</v>
       </c>
       <c r="R9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.52</v>
       </c>
-      <c r="S9" t="n">
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH9" t="n">
         <v>2.36</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.46</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>6.8</v>
+        <v>2.85</v>
       </c>
       <c r="O10" t="n">
-        <v>1.99</v>
+        <v>3.35</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="Q10" t="n">
-        <v>7</v>
+        <v>3.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="S10" t="n">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="T10" t="n">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="V10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="X10" t="n">
-        <v>2.97</v>
+        <v>2.48</v>
       </c>
       <c r="Y10" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.58</v>
+        <v>4.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.36</v>
+        <v>2.07</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.36</v>
+        <v>1.46</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.05</v>
+        <v>3.55</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="N11" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -2088,31 +2088,31 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="M13" t="n">
         <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="O13" t="n">
-        <v>4.9</v>
+        <v>4.81</v>
       </c>
       <c r="P13" t="n">
         <v>2.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="R13" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S13" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="U13" t="n">
         <v>1.73</v>
@@ -2124,25 +2124,25 @@
         <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>5.65</v>
+        <v>5.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="M2" t="n">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="N2" t="n">
-        <v>3.95</v>
+        <v>3.62</v>
       </c>
       <c r="O2" t="n">
         <v>2.3</v>
@@ -684,16 +684,16 @@
         <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="U2" t="n">
         <v>1.46</v>
@@ -705,25 +705,25 @@
         <v>1.2</v>
       </c>
       <c r="X2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45911.22916666666</v>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.94</v>
+        <v>2.49</v>
       </c>
       <c r="M3" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="N3" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="O3" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
         <v>2.01</v>
@@ -819,28 +819,28 @@
         <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="T3" t="n">
         <v>2.9</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AA3" t="n">
         <v>3.6</v>
@@ -849,7 +849,7 @@
         <v>1.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AD3" t="n">
         <v>1.86</v>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45911.375</v>
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1107,10 +1107,10 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45911.44444444445</v>
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1258,10 +1258,10 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45911.5</v>
@@ -1443,22 +1443,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1476,16 +1476,16 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1516,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45911.5</v>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="N9" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="O9" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.72</v>
+        <v>2.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.58</v>
+        <v>2.12</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45911.54166666666</v>
+        <v>45911.55208333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
         <v>2.5</v>
       </c>
-      <c r="M10" t="n">
-        <v>3</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.4</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="V10" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.46</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
-        <v>2.48</v>
+        <v>4.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.52</v>
+        <v>2.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.07</v>
+        <v>1.67</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45911.54166666666</v>
+        <v>45911.55208333334</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.55</v>
+        <v>1.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>1.91</v>
+        <v>6.8</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45911.55208333334</v>
+        <v>45911.57291666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,27 +1918,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.16</v>
+        <v>4.6</v>
       </c>
       <c r="M12" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>9.75</v>
+        <v>1.5</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45911.55208333334</v>
+        <v>45911.58333333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R13" t="n">
         <v>1.5</v>
       </c>
-      <c r="O13" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.2</v>
-      </c>
       <c r="S13" t="n">
-        <v>3.88</v>
+        <v>2.33</v>
       </c>
       <c r="T13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC13" t="n">
         <v>2.05</v>
       </c>
-      <c r="U13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AD13" t="n">
-        <v>2.53</v>
+        <v>1.71</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45911.58333333334</v>
+        <v>45911.625</v>
       </c>
     </row>
     <row r="14">
@@ -2226,52 +2226,52 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -665,7 +665,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -681,31 +681,31 @@
         <v>2.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U2" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X2" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="Y2" t="n">
         <v>1.8</v>
@@ -714,32 +714,32 @@
         <v>1.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="AB2" t="n">
         <v>1.42</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AD2" t="n">
         <v>2.15</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['73', '76']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH2" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AI2" t="n">
         <v>1.57</v>
@@ -798,62 +798,62 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.49</v>
+        <v>2.08</v>
       </c>
       <c r="M3" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.42</v>
+        <v>2.26</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P3" t="n">
-        <v>2.01</v>
+        <v>2.12</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="T3" t="n">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
         <v>1.05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="X3" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AC3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD3" t="n">
         <v>1.9</v>
       </c>
-      <c r="AD3" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AE3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AI3" t="n">
         <v>2.1</v>
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45911.4375</v>
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X5" t="n">
         <v>3.55</v>
       </c>
-      <c r="M5" t="n">
-        <v>4</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="O5" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
       <c r="Y5" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI5" t="n">
         <v>2.5</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="O6" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.33</v>
+        <v>5.4</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.66</v>
+        <v>2.05</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45911.5</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45911.5</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>4.3</v>
       </c>
       <c r="O8" t="n">
-        <v>3.75</v>
+        <v>2.71</v>
       </c>
       <c r="P8" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z8" t="n">
         <v>1.55</v>
       </c>
-      <c r="X8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y8" t="n">
+      <c r="AA8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>2.75</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>2.1</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45911.5</v>
@@ -1581,34 +1581,34 @@
         <v>5.9</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Y9" t="n">
         <v>1.58</v>
@@ -1623,10 +1623,10 @@
         <v>1.64</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45911.55208333334</v>
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.98</v>
+        <v>3.25</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="O10" t="n">
-        <v>4.33</v>
+        <v>3.63</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R10" t="n">
         <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="U10" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W10" t="n">
         <v>1.16</v>
       </c>
       <c r="X10" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>1.8</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45911.55208333334</v>
@@ -1830,43 +1830,43 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3.11</v>
       </c>
       <c r="N11" t="n">
-        <v>6.8</v>
+        <v>3.83</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>2.46</v>
       </c>
       <c r="P11" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>6.22</v>
       </c>
       <c r="R11" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="T11" t="n">
-        <v>3.14</v>
+        <v>3.7</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W11" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="X11" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="Y11" t="n">
         <v>2</v>
@@ -1875,13 +1875,13 @@
         <v>1.72</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.78</v>
+        <v>5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD11" t="n">
         <v>1.53</v>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45911.57291666666</v>
@@ -1968,25 +1968,25 @@
         <v>1.5</v>
       </c>
       <c r="O12" t="n">
-        <v>3.56</v>
+        <v>4.33</v>
       </c>
       <c r="P12" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="U12" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="V12" t="n">
         <v>1.01</v>
@@ -1995,7 +1995,7 @@
         <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>5.5</v>
+        <v>6.05</v>
       </c>
       <c r="Y12" t="n">
         <v>1.4</v>
@@ -2004,16 +2004,16 @@
         <v>2.73</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB12" t="n">
         <v>1.77</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>2.3</v>
+        <v>1.17</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45911.58333333334</v>
@@ -2088,43 +2088,43 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O13" t="n">
         <v>2.5</v>
       </c>
-      <c r="M13" t="n">
-        <v>3</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3.2</v>
-      </c>
       <c r="P13" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.55</v>
+        <v>6</v>
       </c>
       <c r="R13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W13" t="n">
         <v>1.5</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.46</v>
-      </c>
       <c r="X13" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="Y13" t="n">
         <v>2.35</v>
@@ -2133,38 +2133,38 @@
         <v>1.52</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.5</v>
+        <v>4.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AC13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI13" t="n">
         <v>2.05</v>
       </c>
-      <c r="AD13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45911.625</v>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="P14" t="n">
-        <v>2.38</v>
+        <v>2.09</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.05</v>
+        <v>2.31</v>
       </c>
       <c r="R14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.3</v>
       </c>
-      <c r="S14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U14" t="n">
+      <c r="AC14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.5</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45911.875</v>

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -781,20 +781,20 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -856,12 +856,12 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29', '90+3']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['86']</t>
         </is>
       </c>
       <c r="AG3" t="n">
@@ -910,20 +910,20 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -985,12 +985,12 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['37', '41']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AG4" t="n">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1168,48 +1168,48 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.55</v>
+        <v>1.92</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="N6" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="O6" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="P6" t="n">
         <v>1.77</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.4</v>
+        <v>5.35</v>
       </c>
       <c r="R6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="S6" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="T6" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="U6" t="n">
         <v>1.2</v>
@@ -1218,16 +1218,16 @@
         <v>1.1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="X6" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AA6" t="n">
         <v>6</v>
@@ -1236,23 +1236,23 @@
         <v>1.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
+          <t>['45+8']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH6" t="n">
         <v>1.71</v>
@@ -1297,39 +1297,39 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="N7" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="R7" t="n">
         <v>1.65</v>
@@ -1338,53 +1338,53 @@
         <v>2.1</v>
       </c>
       <c r="T7" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W7" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="X7" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.72</v>
+        <v>2.95</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AA7" t="n">
         <v>5.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['26', '72']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AI7" t="n">
         <v>2.25</v>
@@ -1439,32 +1439,32 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>4.3</v>
+        <v>4.95</v>
       </c>
       <c r="O8" t="n">
-        <v>2.71</v>
+        <v>2.98</v>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="Q8" t="n">
         <v>4.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="S8" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="T8" t="n">
         <v>3.6</v>
@@ -1473,31 +1473,31 @@
         <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W8" t="n">
         <v>1.42</v>
       </c>
       <c r="X8" t="n">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.3</v>
+        <v>4.85</v>
       </c>
       <c r="AB8" t="n">
         <v>1.17</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>1.24</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AI8" t="n">
         <v>1.66</v>
@@ -1555,36 +1555,36 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="M9" t="n">
-        <v>4.7</v>
+        <v>6.3</v>
       </c>
       <c r="N9" t="n">
-        <v>5.9</v>
+        <v>10</v>
       </c>
       <c r="O9" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="P9" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="Q9" t="n">
         <v>7</v>
@@ -1593,56 +1593,56 @@
         <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>3.75</v>
+        <v>3.34</v>
       </c>
       <c r="T9" t="n">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="U9" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="V9" t="n">
         <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
+          <t>['35']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG9" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AI9" t="n">
         <v>1.3</v>
@@ -1684,91 +1684,91 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="N10" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="O10" t="n">
-        <v>3.63</v>
+        <v>3.75</v>
       </c>
       <c r="P10" t="n">
         <v>2.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="V10" t="n">
         <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['39', '52']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['59', '90+9']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AH10" t="n">
         <v>1.33</v>
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="M11" t="n">
-        <v>3.11</v>
+        <v>2.87</v>
       </c>
       <c r="N11" t="n">
-        <v>3.83</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="P11" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.22</v>
+        <v>6.07</v>
       </c>
       <c r="R11" t="n">
         <v>1.55</v>
@@ -1860,31 +1860,31 @@
         <v>1.25</v>
       </c>
       <c r="V11" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="W11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Z11" t="n">
         <v>1.46</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.72</v>
       </c>
       <c r="AA11" t="n">
         <v>5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AI11" t="n">
         <v>1.38</v>
@@ -1959,22 +1959,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.6</v>
+        <v>5.12</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="N12" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="O12" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="P12" t="n">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="R12" t="n">
         <v>1.2</v>
@@ -1983,7 +1983,7 @@
         <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="U12" t="n">
         <v>1.76</v>
@@ -1995,19 +1995,19 @@
         <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>6.05</v>
+        <v>6.25</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
         <v>1.44</v>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AI12" t="n">
         <v>2.6</v>
@@ -2088,62 +2088,62 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>2.94</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
         <v>2.5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="S13" t="n">
         <v>2.25</v>
       </c>
       <c r="T13" t="n">
-        <v>3.65</v>
+        <v>3.74</v>
       </c>
       <c r="U13" t="n">
         <v>1.25</v>
       </c>
       <c r="V13" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="X13" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="Z13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.52</v>
       </c>
-      <c r="AA13" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AE13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AI13" t="n">
         <v>2.05</v>
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="O14" t="n">
         <v>4.6</v>
@@ -2232,46 +2232,46 @@
         <v>2.09</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="T14" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="U14" t="n">
         <v>1.53</v>
       </c>
       <c r="V14" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="X14" t="n">
-        <v>3.07</v>
+        <v>3.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.6</v>
+        <v>1.99</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AB14" t="n">
         <v>1.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AI14" t="n">
         <v>2.8</v>

--- a/jogos_2025-09-11.xlsx
+++ b/jogos_2025-09-11.xlsx
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
         <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.92</v>
+        <v>2.64</v>
       </c>
       <c r="M6" t="n">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="N6" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.35</v>
+        <v>3.9</v>
       </c>
       <c r="R6" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="S6" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="T6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="U6" t="n">
         <v>1.2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="W6" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="X6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['26', '72']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>2.1</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['45+8']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45911.5</v>
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.64</v>
+        <v>1.92</v>
       </c>
       <c r="M7" t="n">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="P7" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.9</v>
+        <v>5.35</v>
       </c>
       <c r="R7" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="T7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="U7" t="n">
         <v>1.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="W7" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="X7" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Z7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['45+8']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
         <v>1.36</v>
       </c>
-      <c r="AA7" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>['26', '72']</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>['5']</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.48</v>
+        <v>1.71</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45911.5</v>
@@ -1813,20 +1813,20 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['49', '69']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AG11" t="n">
@@ -1942,20 +1942,20 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['12', '37', '90+8']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -2071,20 +2071,20 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="AG13" t="n">
